--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-allergyintolerance.xlsx
@@ -273,8 +273,8 @@
     <t>物質には、個人に適切な投与量で正しく投与される治療物質が含まれますが、これらに限定されません。食物;植物または動物に由来する材料。または昆虫の刺し傷からの毒。 / Substances include, but are not limited to: a therapeutic substance administered correctly at an appropriate dosage for the individual; food; material derived from plants or animals; or venom from insect stings.</t>
   </si>
   <si>
-    <t>ait-1:AllergyIntolerance.ClinicalStatusが存在する場合は、存在するものとします。 / AllergyIntolerance.clinicalStatus SHALL be present if verificationStatus is not entered-in-error. {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').exists() or clinicalStatus.exists()}
-ait-2:AllergyIntolerance.ClinicalStatusは、検証ステータスが入力されている場合、存在しないでください / AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').empty() or clinicalStatus.empty()}dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>ait-1:AllergyIntolerance.verificationStatusに'entered-in-error'が入力されていない場合には、AllergyIntolerance.ClinicalStatusは、存在しなければならない。/ AllergyIntolerance.clinicalStatus SHALL be present if verificationStatus is not entered-in-error. {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').exists() or clinicalStatus.exists()}
+ait-2:AllergyIntolerance.verificationStatusに'entered-in-error'が入力されている場合、AllergyIntolerance.ClinicalStatusは、存在してはならない。 / AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').empty() or clinicalStatus.empty()}dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照しなければならない。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはあってはならない。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
@@ -312,16 +312,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -447,7 +447,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -478,10 +478,10 @@
     <t>このアイテムの外部ID / External ids for this item</t>
   </si>
   <si>
-    <t>リソースが更新され、サーバーからサーバーに伝播するにつれて一定のままであるパフォーマーまたは他のシステムによってこのアレルギー耐性に割り当てられたビジネス識別子。 / Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません（[ディスカッション]（Resource.html＃識別子を参照））。識別子が単一のリソースインスタンスにのみ表示することがベストプラクティスですが、ビジネス慣行は、同じ識別子を持つ複数のリソースインスタンスが存在する可能性があることを時々決定する場合があります。たとえば、複数の患者と個人のリソースインスタンスは、同じ社会保険番号を共有する場合があります。 / This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>リソースが更新され、サーバーからサーバーに伝播するにつれて一定のままであるパフォーマーまたは他のシステムによってこのアレルギー耐性に割り当てられたビジネスidentifier。 / Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません（[ディスカッション]（Resource.html＃identifierを参照））。identifierが単一のリソースインスタンスにのみ表示することがベストプラクティスですが、ビジネス慣行は、同じidentifierを持つ複数のリソースインスタンスが存在する可能性があることを時々決定する場合があります。たとえば、複数の患者と個人のリソースインスタンスは、同じ社会保険番号を共有する場合があります。 / This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
   </si>
   <si>
     <t>さまざまな参加システムで知られており、サーバー全体で一貫している方法でアレルギー耐性を識別できるようにします。 / Allows identification of the AllergyIntolerance as it is known by various participating systems and in a way that remains consistent across servers.</t>
